--- a/Tests/Validation/Wheat/data/FAR TAS W21-03-1.xlsx
+++ b/Tests/Validation/Wheat/data/FAR TAS W21-03-1.xlsx
@@ -1,32 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Observed" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observed" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,16 +48,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -417,126 +430,111 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X146"/>
+  <dimension ref="A1:U146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>SimulationName</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Clock.Today</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Phenology.CurrentStageName</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Mgmt</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Wheat.SowingData.Cultivar</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Potential</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>NDVIModel.Script.NDVI</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>NDVIModel.Script.NDVI.se</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Wheat.AboveGround.Wt</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Wheat.AboveGround.Wt.se</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Size</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Size.se</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Wheat.SowingData.Population</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Wheat.SowingData.Population.se</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Wheat.Population</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Wheat.Population.se</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Density</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Density.se</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Wheat.Grain.Moisture</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Wheat.Grain.WaterContent</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Moisture.se</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Protein</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Protein.se</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Screenings</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Screenings.se</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Wt</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Wt.se</t>
         </is>
@@ -548,31 +546,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvAccroc</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="3" t="n">
         <v>44404</v>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
+      <c r="D2" t="n">
         <v>0.63</v>
       </c>
-      <c r="H2" t="n">
+      <c r="E2" t="n">
         <v>0.0122474487139159</v>
       </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -586,9 +572,6 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -596,31 +579,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvAccroc</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="3" t="n">
         <v>44469</v>
       </c>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+      <c r="D3" t="n">
         <v>0.86</v>
       </c>
-      <c r="H3" t="n">
+      <c r="E3" t="n">
         <v>0</v>
       </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -634,9 +605,6 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -644,31 +612,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvAccroc</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="3" t="n">
         <v>44512</v>
       </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
+      <c r="D4" t="n">
         <v>0.7825</v>
       </c>
-      <c r="H4" t="n">
+      <c r="E4" t="n">
         <v>0.0025</v>
       </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -682,9 +638,6 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -692,31 +645,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvAccroc</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="3" t="n">
         <v>44543</v>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
+      <c r="D5" t="n">
         <v>0.4125</v>
       </c>
-      <c r="H5" t="n">
+      <c r="E5" t="n">
         <v>0.0110867789130417</v>
       </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -730,9 +671,6 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -740,7 +678,7 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvAccroc</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="3" t="n">
         <v>44565</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,27 +686,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
+      <c r="D6" t="n">
         <v>0.13</v>
       </c>
-      <c r="H6" t="n">
+      <c r="E6" t="n">
         <v>0</v>
       </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -782,9 +708,6 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -792,7 +715,7 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvAccroc</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="3" t="n">
         <v>44579</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -800,31 +723,19 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>0.0506256489652609</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.704293089104301</v>
+      </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>0.0506256489652609</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.704293089104301</v>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -834,9 +745,6 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -844,7 +752,7 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvAccroc</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="3" t="n">
         <v>44581</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -852,57 +760,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>75.693</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.492957401810749</v>
+      </c>
+      <c r="N8" t="n">
+        <v>11.825</v>
+      </c>
       <c r="O8" t="n">
-        <v>75.693</v>
+        <v>0.372771154105751</v>
       </c>
       <c r="P8" t="n">
-        <v>0.492957401810749</v>
+        <v>11.725</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.825</v>
+        <v>0.306526235962492</v>
       </c>
       <c r="R8" t="n">
-        <v>0.372771154105751</v>
+        <v>1.39313001884355</v>
       </c>
       <c r="S8" t="n">
-        <v>11.725</v>
+        <v>0.228552498050978</v>
       </c>
       <c r="T8" t="n">
-        <v>0.306526235962492</v>
+        <v>1301.11437246964</v>
       </c>
       <c r="U8" t="n">
-        <v>1.39313001884355</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.228552498050978</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1301.11437246964</v>
-      </c>
-      <c r="X8" t="n">
         <v>0.106469672690328</v>
       </c>
     </row>
@@ -912,31 +805,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvScepter</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="3" t="n">
         <v>44404</v>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
+      <c r="D9" t="n">
         <v>0.59</v>
       </c>
-      <c r="H9" t="n">
+      <c r="E9" t="n">
         <v>0.0204124145231932</v>
       </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -950,9 +831,6 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -960,31 +838,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvScepter</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="3" t="n">
         <v>44469</v>
       </c>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
+      <c r="D10" t="n">
         <v>0.7975</v>
       </c>
-      <c r="H10" t="n">
+      <c r="E10" t="n">
         <v>0.0131497781983829</v>
       </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -998,9 +864,6 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1008,31 +871,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvScepter</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="3" t="n">
         <v>44512</v>
       </c>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
+      <c r="D11" t="n">
         <v>0.715</v>
       </c>
-      <c r="H11" t="n">
+      <c r="E11" t="n">
         <v>0.015</v>
       </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -1046,9 +897,6 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1056,31 +904,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvScepter</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="3" t="n">
         <v>44543</v>
       </c>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
+      <c r="D12" t="n">
         <v>0.39</v>
       </c>
-      <c r="H12" t="n">
+      <c r="E12" t="n">
         <v>0.0177951304200522</v>
       </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -1094,9 +930,6 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1104,7 +937,7 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvScepter</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="3" t="n">
         <v>44565</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -1112,27 +945,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
+      <c r="D13" t="n">
         <v>0.1625</v>
       </c>
-      <c r="H13" t="n">
+      <c r="E13" t="n">
         <v>0.0025</v>
       </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -1146,9 +967,6 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1156,7 +974,7 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvScepter</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="3" t="n">
         <v>44581</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -1164,57 +982,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>75.437</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.32695805007795</v>
+      </c>
+      <c r="N14" t="n">
+        <v>11.975</v>
+      </c>
       <c r="O14" t="n">
-        <v>75.437</v>
+        <v>0.309232921921325</v>
       </c>
       <c r="P14" t="n">
-        <v>1.32695805007795</v>
+        <v>14.775</v>
       </c>
       <c r="Q14" t="n">
-        <v>11.975</v>
+        <v>0.193110503770941</v>
       </c>
       <c r="R14" t="n">
-        <v>0.309232921921325</v>
+        <v>1.45452699177663</v>
       </c>
       <c r="S14" t="n">
-        <v>14.775</v>
+        <v>0.265897055681019</v>
       </c>
       <c r="T14" t="n">
-        <v>0.193110503770941</v>
+        <v>767.123178137652</v>
       </c>
       <c r="U14" t="n">
-        <v>1.45452699177663</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.265897055681019</v>
-      </c>
-      <c r="W14" t="n">
-        <v>767.123178137652</v>
-      </c>
-      <c r="X14" t="n">
         <v>0.7271559041547579</v>
       </c>
     </row>
@@ -1224,31 +1027,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvAnapurna</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="3" t="n">
         <v>44404</v>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
+      <c r="D15" t="n">
         <v>0.665</v>
       </c>
-      <c r="H15" t="n">
+      <c r="E15" t="n">
         <v>0.00957427107756339</v>
       </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1262,9 +1053,6 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1272,31 +1060,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvAnapurna</t>
         </is>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="3" t="n">
         <v>44469</v>
       </c>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
+      <c r="D16" t="n">
         <v>0.84</v>
       </c>
-      <c r="H16" t="n">
+      <c r="E16" t="n">
         <v>0.00707106781186548</v>
       </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1310,9 +1086,6 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1320,31 +1093,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvAnapurna</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="3" t="n">
         <v>44512</v>
       </c>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
+      <c r="D17" t="n">
         <v>0.7575</v>
       </c>
-      <c r="H17" t="n">
+      <c r="E17" t="n">
         <v>0.00750000000000002</v>
       </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1358,9 +1119,6 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1368,31 +1126,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvAnapurna</t>
         </is>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="3" t="n">
         <v>44543</v>
       </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
+      <c r="D18" t="n">
         <v>0.4525</v>
       </c>
-      <c r="H18" t="n">
+      <c r="E18" t="n">
         <v>0.0025</v>
       </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1406,9 +1152,6 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1416,7 +1159,7 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvAnapurna</t>
         </is>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="3" t="n">
         <v>44565</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -1424,27 +1167,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
+      <c r="D19" t="n">
         <v>0.1275</v>
       </c>
-      <c r="H19" t="n">
+      <c r="E19" t="n">
         <v>0.00478713553878169</v>
       </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1458,9 +1189,6 @@
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1468,7 +1196,7 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvAnapurna</t>
         </is>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="3" t="n">
         <v>44579</v>
       </c>
       <c r="C20" t="inlineStr">
@@ -1476,31 +1204,19 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>0.0511172465215943</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.49638017832077</v>
+      </c>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
-        <v>0.0511172465215943</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.49638017832077</v>
-      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -1510,9 +1226,6 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1520,7 +1233,7 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvAnapurna</t>
         </is>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="3" t="n">
         <v>44581</v>
       </c>
       <c r="C21" t="inlineStr">
@@ -1528,57 +1241,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>77.66500000000001</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.513594197786539</v>
+      </c>
+      <c r="N21" t="n">
+        <v>11.875</v>
+      </c>
       <c r="O21" t="n">
-        <v>77.66500000000001</v>
+        <v>0.314576434802948</v>
       </c>
       <c r="P21" t="n">
-        <v>0.513594197786539</v>
+        <v>12.925</v>
       </c>
       <c r="Q21" t="n">
-        <v>11.875</v>
+        <v>0.193110503770941</v>
       </c>
       <c r="R21" t="n">
-        <v>0.314576434802948</v>
+        <v>2.06226471227199</v>
       </c>
       <c r="S21" t="n">
-        <v>12.925</v>
+        <v>0.387005190888335</v>
       </c>
       <c r="T21" t="n">
-        <v>0.193110503770941</v>
+        <v>1270.4866734143</v>
       </c>
       <c r="U21" t="n">
-        <v>2.06226471227199</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0.387005190888335</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1270.4866734143</v>
-      </c>
-      <c r="X21" t="n">
         <v>0.22442767078946</v>
       </c>
     </row>
@@ -1588,31 +1286,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvTrojan</t>
         </is>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="3" t="n">
         <v>44404</v>
       </c>
       <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
+      <c r="D22" t="n">
         <v>0.643333333333333</v>
       </c>
-      <c r="H22" t="n">
+      <c r="E22" t="n">
         <v>0.0333333333333333</v>
       </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -1626,9 +1312,6 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1636,31 +1319,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvTrojan</t>
         </is>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="3" t="n">
         <v>44469</v>
       </c>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
+      <c r="D23" t="n">
         <v>0.8075</v>
       </c>
-      <c r="H23" t="n">
+      <c r="E23" t="n">
         <v>0.0110867789130417</v>
       </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -1674,9 +1345,6 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1684,31 +1352,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvTrojan</t>
         </is>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="3" t="n">
         <v>44512</v>
       </c>
       <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
+      <c r="D24" t="n">
         <v>0.745</v>
       </c>
-      <c r="H24" t="n">
+      <c r="E24" t="n">
         <v>0.005</v>
       </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -1722,9 +1378,6 @@
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1732,31 +1385,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvTrojan</t>
         </is>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="3" t="n">
         <v>44543</v>
       </c>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
+      <c r="D25" t="n">
         <v>0.5175</v>
       </c>
-      <c r="H25" t="n">
+      <c r="E25" t="n">
         <v>0.0131497781983829</v>
       </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -1770,9 +1411,6 @@
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1780,7 +1418,7 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvTrojan</t>
         </is>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="3" t="n">
         <v>44565</v>
       </c>
       <c r="C26" t="inlineStr">
@@ -1788,27 +1426,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
+      <c r="D26" t="n">
         <v>0.1675</v>
       </c>
-      <c r="H26" t="n">
+      <c r="E26" t="n">
         <v>0.0025</v>
       </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -1822,9 +1448,6 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1832,7 +1455,7 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvTrojan</t>
         </is>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="3" t="n">
         <v>44581</v>
       </c>
       <c r="C27" t="inlineStr">
@@ -1840,57 +1463,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>76.6985</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.552245341009471</v>
+      </c>
+      <c r="N27" t="n">
+        <v>11.875</v>
+      </c>
       <c r="O27" t="n">
-        <v>76.6985</v>
+        <v>0.249582985531199</v>
       </c>
       <c r="P27" t="n">
-        <v>0.552245341009471</v>
+        <v>13.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>11.875</v>
+        <v>0.221735578260834</v>
       </c>
       <c r="R27" t="n">
-        <v>0.249582985531199</v>
+        <v>1.27047412546946</v>
       </c>
       <c r="S27" t="n">
-        <v>13.45</v>
+        <v>0.186402878846359</v>
       </c>
       <c r="T27" t="n">
-        <v>0.221735578260834</v>
+        <v>924.990294646874</v>
       </c>
       <c r="U27" t="n">
-        <v>1.27047412546946</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0.186402878846359</v>
-      </c>
-      <c r="W27" t="n">
-        <v>924.990294646874</v>
-      </c>
-      <c r="X27" t="n">
         <v>0.947930085426435</v>
       </c>
     </row>
@@ -1900,31 +1508,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvCesario</t>
         </is>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="3" t="n">
         <v>44404</v>
       </c>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Cesario</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
+      <c r="D28" t="n">
         <v>0.655</v>
       </c>
-      <c r="H28" t="n">
+      <c r="E28" t="n">
         <v>0.00957427107756339</v>
       </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -1938,9 +1534,6 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1948,31 +1541,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvCesario</t>
         </is>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="3" t="n">
         <v>44469</v>
       </c>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Cesario</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
+      <c r="D29" t="n">
         <v>0.8725000000000001</v>
       </c>
-      <c r="H29" t="n">
+      <c r="E29" t="n">
         <v>0.0025</v>
       </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -1986,9 +1567,6 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1996,31 +1574,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvCesario</t>
         </is>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="3" t="n">
         <v>44512</v>
       </c>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Cesario</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
+      <c r="D30" t="n">
         <v>0.8025</v>
       </c>
-      <c r="H30" t="n">
+      <c r="E30" t="n">
         <v>0.00250000000000001</v>
       </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -2034,9 +1600,6 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2044,31 +1607,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvCesario</t>
         </is>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="3" t="n">
         <v>44543</v>
       </c>
       <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Cesario</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
+      <c r="D31" t="n">
         <v>0.5649999999999999</v>
       </c>
-      <c r="H31" t="n">
+      <c r="E31" t="n">
         <v>0.00957427107756335</v>
       </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -2082,9 +1633,6 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2092,7 +1640,7 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvCesario</t>
         </is>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="3" t="n">
         <v>44565</v>
       </c>
       <c r="C32" t="inlineStr">
@@ -2100,27 +1648,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Cesario</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
+      <c r="D32" t="n">
         <v>0.14</v>
       </c>
-      <c r="H32" t="n">
+      <c r="E32" t="n">
         <v>0</v>
       </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -2134,9 +1670,6 @@
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2144,7 +1677,7 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvCesario</t>
         </is>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="3" t="n">
         <v>44579</v>
       </c>
       <c r="C33" t="inlineStr">
@@ -2152,31 +1685,19 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Cesario</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+      <c r="H33" t="n">
+        <v>0.0473873151549099</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.274697951633894</v>
+      </c>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="n">
-        <v>0.0473873151549099</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0.274697951633894</v>
-      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -2186,9 +1707,6 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2196,7 +1714,7 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvCesario</t>
         </is>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="3" t="n">
         <v>44581</v>
       </c>
       <c r="C34" t="inlineStr">
@@ -2204,57 +1722,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Cesario</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>78.02549999999999</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.146044228460652</v>
+      </c>
+      <c r="N34" t="n">
+        <v>11.95</v>
+      </c>
       <c r="O34" t="n">
-        <v>78.02549999999999</v>
+        <v>0.221735578260834</v>
       </c>
       <c r="P34" t="n">
-        <v>0.146044228460652</v>
+        <v>11.85</v>
       </c>
       <c r="Q34" t="n">
-        <v>11.95</v>
+        <v>0.184842275106823</v>
       </c>
       <c r="R34" t="n">
-        <v>0.221735578260834</v>
+        <v>1.07263788808103</v>
       </c>
       <c r="S34" t="n">
-        <v>11.85</v>
+        <v>0.155622912570743</v>
       </c>
       <c r="T34" t="n">
-        <v>0.184842275106823</v>
+        <v>1326.26390013495</v>
       </c>
       <c r="U34" t="n">
-        <v>1.07263788808103</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0.155622912570743</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1326.26390013495</v>
-      </c>
-      <c r="X34" t="n">
         <v>0.280878671836203</v>
       </c>
     </row>
@@ -2264,31 +1767,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvTabasco</t>
         </is>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="3" t="n">
         <v>44404</v>
       </c>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Tabasco</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
+      <c r="D35" t="n">
         <v>0.5425</v>
       </c>
-      <c r="H35" t="n">
+      <c r="E35" t="n">
         <v>0.0103077640640441</v>
       </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
@@ -2302,9 +1793,6 @@
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2312,31 +1800,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvTabasco</t>
         </is>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="3" t="n">
         <v>44469</v>
       </c>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Tabasco</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
+      <c r="D36" t="n">
         <v>0.8625</v>
       </c>
-      <c r="H36" t="n">
+      <c r="E36" t="n">
         <v>0.0025</v>
       </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -2350,9 +1826,6 @@
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2360,31 +1833,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvTabasco</t>
         </is>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="3" t="n">
         <v>44512</v>
       </c>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Tabasco</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
+      <c r="D37" t="n">
         <v>0.85</v>
       </c>
-      <c r="H37" t="n">
+      <c r="E37" t="n">
         <v>0.00408248290463863</v>
       </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
@@ -2398,9 +1859,6 @@
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2408,31 +1866,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvTabasco</t>
         </is>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="3" t="n">
         <v>44543</v>
       </c>
       <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Tabasco</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
+      <c r="D38" t="n">
         <v>0.6425</v>
       </c>
-      <c r="H38" t="n">
+      <c r="E38" t="n">
         <v>0.0278013788626871</v>
       </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
@@ -2446,9 +1892,6 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2456,7 +1899,7 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvTabasco</t>
         </is>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="3" t="n">
         <v>44565</v>
       </c>
       <c r="C39" t="inlineStr">
@@ -2464,27 +1907,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Tabasco</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
+      <c r="D39" t="n">
         <v>0.1775</v>
       </c>
-      <c r="H39" t="n">
+      <c r="E39" t="n">
         <v>0.00478713553878169</v>
       </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
@@ -2498,9 +1929,6 @@
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2508,7 +1936,7 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvTabasco</t>
         </is>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="3" t="n">
         <v>44579</v>
       </c>
       <c r="C40" t="inlineStr">
@@ -2516,31 +1944,19 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Tabasco</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+      <c r="H40" t="n">
+        <v>0.0441728206758966</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3.34672027630068</v>
+      </c>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="n">
-        <v>0.0441728206758966</v>
-      </c>
-      <c r="L40" t="n">
-        <v>3.34672027630068</v>
-      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
@@ -2550,9 +1966,6 @@
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2560,7 +1973,7 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvTabasco</t>
         </is>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="3" t="n">
         <v>44581</v>
       </c>
       <c r="C41" t="inlineStr">
@@ -2568,57 +1981,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Tabasco</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="L41" t="n">
+        <v>73.352</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.546613208768323</v>
+      </c>
+      <c r="N41" t="n">
+        <v>11.175</v>
+      </c>
       <c r="O41" t="n">
-        <v>73.352</v>
+        <v>0.193110503770941</v>
       </c>
       <c r="P41" t="n">
-        <v>0.546613208768323</v>
+        <v>11.425</v>
       </c>
       <c r="Q41" t="n">
-        <v>11.175</v>
+        <v>0.340036762718386</v>
       </c>
       <c r="R41" t="n">
-        <v>0.193110503770941</v>
+        <v>3.49553556650078</v>
       </c>
       <c r="S41" t="n">
-        <v>11.425</v>
+        <v>0.519994319215268</v>
       </c>
       <c r="T41" t="n">
-        <v>0.340036762718386</v>
+        <v>1096.27240215924</v>
       </c>
       <c r="U41" t="n">
-        <v>3.49553556650078</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0.519994319215268</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1096.27240215924</v>
-      </c>
-      <c r="X41" t="n">
         <v>0.09148836915066259</v>
       </c>
     </row>
@@ -2628,31 +2026,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvBig Red</t>
         </is>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="3" t="n">
         <v>44404</v>
       </c>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Big Red</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
+      <c r="D42" t="n">
         <v>0.575</v>
       </c>
-      <c r="H42" t="n">
+      <c r="E42" t="n">
         <v>0.0144337567297406</v>
       </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
@@ -2666,9 +2052,6 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2676,31 +2059,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvBig Red</t>
         </is>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="3" t="n">
         <v>44469</v>
       </c>
       <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Big Red</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
+      <c r="D43" t="n">
         <v>0.845</v>
       </c>
-      <c r="H43" t="n">
+      <c r="E43" t="n">
         <v>0.00957427107756339</v>
       </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -2714,9 +2085,6 @@
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2724,31 +2092,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvBig Red</t>
         </is>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="3" t="n">
         <v>44512</v>
       </c>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Big Red</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
+      <c r="D44" t="n">
         <v>0.79</v>
       </c>
-      <c r="H44" t="n">
+      <c r="E44" t="n">
         <v>0.00408248290463863</v>
       </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -2762,9 +2118,6 @@
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2772,31 +2125,19 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvBig Red</t>
         </is>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="3" t="n">
         <v>44543</v>
       </c>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Big Red</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
+      <c r="D45" t="n">
         <v>0.5475</v>
       </c>
-      <c r="H45" t="n">
+      <c r="E45" t="n">
         <v>0.00629152869605898</v>
       </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -2810,9 +2151,6 @@
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2820,7 +2158,7 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvBig Red</t>
         </is>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="3" t="n">
         <v>44565</v>
       </c>
       <c r="C46" t="inlineStr">
@@ -2828,27 +2166,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Big Red</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
+      <c r="D46" t="n">
         <v>0.13</v>
       </c>
-      <c r="H46" t="n">
+      <c r="E46" t="n">
         <v>0.00408248290463863</v>
       </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -2862,9 +2188,6 @@
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2872,7 +2195,7 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvBig Red</t>
         </is>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="3" t="n">
         <v>44579</v>
       </c>
       <c r="C47" t="inlineStr">
@@ -2880,31 +2203,19 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Big Red</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+      <c r="H47" t="n">
+        <v>0.0532945522120373</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1.59146030283647</v>
+      </c>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="n">
-        <v>0.0532945522120373</v>
-      </c>
-      <c r="L47" t="n">
-        <v>1.59146030283647</v>
-      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
@@ -2914,9 +2225,6 @@
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2924,7 +2232,7 @@
           <t>FAR TAS W21-03-1MgmtHigh InputCvBig Red</t>
         </is>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="3" t="n">
         <v>44581</v>
       </c>
       <c r="C48" t="inlineStr">
@@ -2932,57 +2240,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Big Red</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="L48" t="n">
+        <v>79.86450000000001</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.276367358178687</v>
+      </c>
+      <c r="N48" t="n">
+        <v>12.125</v>
+      </c>
       <c r="O48" t="n">
-        <v>79.86450000000001</v>
+        <v>0.217466472511665</v>
       </c>
       <c r="P48" t="n">
-        <v>0.276367358178687</v>
+        <v>11.5</v>
       </c>
       <c r="Q48" t="n">
-        <v>12.125</v>
+        <v>0.0408248290463863</v>
       </c>
       <c r="R48" t="n">
-        <v>0.217466472511665</v>
+        <v>1.95463033230365</v>
       </c>
       <c r="S48" t="n">
-        <v>11.5</v>
+        <v>0.512238648703073</v>
       </c>
       <c r="T48" t="n">
-        <v>0.0408248290463863</v>
+        <v>1297.58157894737</v>
       </c>
       <c r="U48" t="n">
-        <v>1.95463033230365</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0.512238648703073</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1297.58157894737</v>
-      </c>
-      <c r="X48" t="n">
         <v>0.0963951432908971</v>
       </c>
     </row>
@@ -2992,37 +2285,25 @@
           <t>FAR TAS W21-03-1MgmtStandardCvAccroc</t>
         </is>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="3" t="n">
         <v>44347</v>
       </c>
       <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="J49" t="n">
+        <v>172.5</v>
+      </c>
+      <c r="K49" t="n">
+        <v>8.2915619758885</v>
+      </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="n">
-        <v>172.5</v>
-      </c>
-      <c r="N49" t="n">
-        <v>8.2915619758885</v>
-      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
@@ -3030,9 +2311,6 @@
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3040,31 +2318,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvAccroc</t>
         </is>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="3" t="n">
         <v>44404</v>
       </c>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
+      <c r="D50" t="n">
         <v>0.605</v>
       </c>
-      <c r="H50" t="n">
+      <c r="E50" t="n">
         <v>0.00866025403784439</v>
       </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
@@ -3078,9 +2344,6 @@
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3088,31 +2351,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvAccroc</t>
         </is>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="3" t="n">
         <v>44469</v>
       </c>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
+      <c r="D51" t="n">
         <v>0.8425</v>
       </c>
-      <c r="H51" t="n">
+      <c r="E51" t="n">
         <v>0.0025</v>
       </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
@@ -3126,9 +2377,6 @@
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3136,31 +2384,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvAccroc</t>
         </is>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="3" t="n">
         <v>44512</v>
       </c>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
+      <c r="D52" t="n">
         <v>0.7775</v>
       </c>
-      <c r="H52" t="n">
+      <c r="E52" t="n">
         <v>0.00250000000000001</v>
       </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
@@ -3174,9 +2410,6 @@
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3184,31 +2417,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvAccroc</t>
         </is>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="3" t="n">
         <v>44543</v>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
+      <c r="D53" t="n">
         <v>0.365</v>
       </c>
-      <c r="H53" t="n">
+      <c r="E53" t="n">
         <v>0.0119023807142381</v>
       </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
@@ -3222,9 +2443,6 @@
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3232,7 +2450,7 @@
           <t>FAR TAS W21-03-1MgmtStandardCvAccroc</t>
         </is>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="3" t="n">
         <v>44565</v>
       </c>
       <c r="C54" t="inlineStr">
@@ -3240,27 +2458,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
+      <c r="D54" t="n">
         <v>0.1275</v>
       </c>
-      <c r="H54" t="n">
+      <c r="E54" t="n">
         <v>0.00629152869605896</v>
       </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
@@ -3274,9 +2480,6 @@
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3284,7 +2487,7 @@
           <t>FAR TAS W21-03-1MgmtStandardCvAccroc</t>
         </is>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="3" t="n">
         <v>44581</v>
       </c>
       <c r="C55" t="inlineStr">
@@ -3292,57 +2495,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="L55" t="n">
+        <v>74.1015</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.84363158428309</v>
+      </c>
+      <c r="N55" t="n">
+        <v>11.425</v>
+      </c>
       <c r="O55" t="n">
-        <v>74.1015</v>
+        <v>0.0478713553878168</v>
       </c>
       <c r="P55" t="n">
-        <v>0.84363158428309</v>
+        <v>10.825</v>
       </c>
       <c r="Q55" t="n">
-        <v>11.425</v>
+        <v>0.103077640640442</v>
       </c>
       <c r="R55" t="n">
-        <v>0.0478713553878168</v>
+        <v>1.92346786865371</v>
       </c>
       <c r="S55" t="n">
-        <v>10.825</v>
+        <v>0.147856172770837</v>
       </c>
       <c r="T55" t="n">
-        <v>0.103077640640442</v>
+        <v>1166.42582644628</v>
       </c>
       <c r="U55" t="n">
-        <v>1.92346786865371</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0.147856172770837</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1166.42582644628</v>
-      </c>
-      <c r="X55" t="n">
         <v>0.121071769430452</v>
       </c>
     </row>
@@ -3352,37 +2540,25 @@
           <t>FAR TAS W21-03-1MgmtStandardCvTrojan</t>
         </is>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="3" t="n">
         <v>44347</v>
       </c>
       <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+      <c r="J56" t="n">
+        <v>164.375</v>
+      </c>
+      <c r="K56" t="n">
+        <v>7.31543744419977</v>
+      </c>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="n">
-        <v>164.375</v>
-      </c>
-      <c r="N56" t="n">
-        <v>7.31543744419977</v>
-      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
@@ -3390,9 +2566,6 @@
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3400,31 +2573,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvTrojan</t>
         </is>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="3" t="n">
         <v>44404</v>
       </c>
       <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
+      <c r="D57" t="n">
         <v>0.5925</v>
       </c>
-      <c r="H57" t="n">
+      <c r="E57" t="n">
         <v>0.00853912563829968</v>
       </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
@@ -3438,9 +2599,6 @@
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3448,31 +2606,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvTrojan</t>
         </is>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="3" t="n">
         <v>44469</v>
       </c>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
+      <c r="D58" t="n">
         <v>0.8325</v>
       </c>
-      <c r="H58" t="n">
+      <c r="E58" t="n">
         <v>0.00478713553878169</v>
       </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
@@ -3486,9 +2632,6 @@
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3496,31 +2639,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvTrojan</t>
         </is>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="3" t="n">
         <v>44512</v>
       </c>
       <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
+      <c r="D59" t="n">
         <v>0.7475000000000001</v>
       </c>
-      <c r="H59" t="n">
+      <c r="E59" t="n">
         <v>0.00249999999999999</v>
       </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
@@ -3534,9 +2665,6 @@
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
-      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3544,31 +2672,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvTrojan</t>
         </is>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="3" t="n">
         <v>44543</v>
       </c>
       <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
+      <c r="D60" t="n">
         <v>0.3875</v>
       </c>
-      <c r="H60" t="n">
+      <c r="E60" t="n">
         <v>0.0165201896679992</v>
       </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
@@ -3582,9 +2698,6 @@
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
-      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3592,7 +2705,7 @@
           <t>FAR TAS W21-03-1MgmtStandardCvTrojan</t>
         </is>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="3" t="n">
         <v>44565</v>
       </c>
       <c r="C61" t="inlineStr">
@@ -3600,27 +2713,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G61" t="n">
+      <c r="D61" t="n">
         <v>0.1525</v>
       </c>
-      <c r="H61" t="n">
+      <c r="E61" t="n">
         <v>0.0025</v>
       </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
@@ -3634,9 +2735,6 @@
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
-      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3644,7 +2742,7 @@
           <t>FAR TAS W21-03-1MgmtStandardCvTrojan</t>
         </is>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="3" t="n">
         <v>44581</v>
       </c>
       <c r="C62" t="inlineStr">
@@ -3652,57 +2750,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="L62" t="n">
+        <v>69.648</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1.82373919919123</v>
+      </c>
+      <c r="N62" t="n">
+        <v>11.575</v>
+      </c>
       <c r="O62" t="n">
-        <v>69.648</v>
+        <v>0.0629152869605895</v>
       </c>
       <c r="P62" t="n">
-        <v>1.82373919919123</v>
+        <v>14.35</v>
       </c>
       <c r="Q62" t="n">
-        <v>11.575</v>
+        <v>0.08660254037844391</v>
       </c>
       <c r="R62" t="n">
-        <v>0.0629152869605895</v>
+        <v>2.36928345616674</v>
       </c>
       <c r="S62" t="n">
-        <v>14.35</v>
+        <v>0.207089577774021</v>
       </c>
       <c r="T62" t="n">
-        <v>0.08660254037844391</v>
+        <v>583.518422865014</v>
       </c>
       <c r="U62" t="n">
-        <v>2.36928345616674</v>
-      </c>
-      <c r="V62" t="n">
-        <v>0.207089577774021</v>
-      </c>
-      <c r="W62" t="n">
-        <v>583.518422865014</v>
-      </c>
-      <c r="X62" t="n">
         <v>0.242399172538703</v>
       </c>
     </row>
@@ -3712,37 +2795,25 @@
           <t>FAR TAS W21-03-1MgmtStandardCvBig Red</t>
         </is>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="3" t="n">
         <v>44347</v>
       </c>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Big Red</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+      <c r="J63" t="n">
+        <v>158.125</v>
+      </c>
+      <c r="K63" t="n">
+        <v>11.3823236497064</v>
+      </c>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="n">
-        <v>158.125</v>
-      </c>
-      <c r="N63" t="n">
-        <v>11.3823236497064</v>
-      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
@@ -3750,9 +2821,6 @@
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3760,31 +2828,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvBig Red</t>
         </is>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="3" t="n">
         <v>44404</v>
       </c>
       <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Big Red</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G64" t="n">
+      <c r="D64" t="n">
         <v>0.6</v>
       </c>
-      <c r="H64" t="n">
+      <c r="E64" t="n">
         <v>0.0187082869338697</v>
       </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
@@ -3798,9 +2854,6 @@
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
-      <c r="X64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3808,31 +2861,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvBig Red</t>
         </is>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="3" t="n">
         <v>44469</v>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Big Red</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G65" t="n">
+      <c r="D65" t="n">
         <v>0.86</v>
       </c>
-      <c r="H65" t="n">
+      <c r="E65" t="n">
         <v>0.00408248290463863</v>
       </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
@@ -3846,9 +2887,6 @@
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3856,31 +2894,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvBig Red</t>
         </is>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="3" t="n">
         <v>44512</v>
       </c>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Big Red</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G66" t="n">
+      <c r="D66" t="n">
         <v>0.7975</v>
       </c>
-      <c r="H66" t="n">
+      <c r="E66" t="n">
         <v>0.00478713553878169</v>
       </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
@@ -3894,9 +2920,6 @@
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
-      <c r="X66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3904,31 +2927,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvBig Red</t>
         </is>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="3" t="n">
         <v>44543</v>
       </c>
       <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Big Red</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G67" t="n">
+      <c r="D67" t="n">
         <v>0.4875</v>
       </c>
-      <c r="H67" t="n">
+      <c r="E67" t="n">
         <v>0.00750000000000001</v>
       </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
@@ -3942,9 +2953,6 @@
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
-      <c r="X67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3952,7 +2960,7 @@
           <t>FAR TAS W21-03-1MgmtStandardCvBig Red</t>
         </is>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="3" t="n">
         <v>44565</v>
       </c>
       <c r="C68" t="inlineStr">
@@ -3960,27 +2968,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Big Red</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G68" t="n">
+      <c r="D68" t="n">
         <v>0.1275</v>
       </c>
-      <c r="H68" t="n">
+      <c r="E68" t="n">
         <v>0.00478713553878169</v>
       </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
@@ -3994,9 +2990,6 @@
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr"/>
-      <c r="X68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4004,7 +2997,7 @@
           <t>FAR TAS W21-03-1MgmtStandardCvBig Red</t>
         </is>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="3" t="n">
         <v>44581</v>
       </c>
       <c r="C69" t="inlineStr">
@@ -4012,57 +3005,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Big Red</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+      <c r="L69" t="n">
+        <v>77.84099999999999</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.769108791611</v>
+      </c>
+      <c r="N69" t="n">
+        <v>11.9</v>
+      </c>
       <c r="O69" t="n">
-        <v>77.84099999999999</v>
+        <v>0.135400640077266</v>
       </c>
       <c r="P69" t="n">
-        <v>0.769108791611</v>
+        <v>11.275</v>
       </c>
       <c r="Q69" t="n">
-        <v>11.9</v>
+        <v>0.286865241300975</v>
       </c>
       <c r="R69" t="n">
-        <v>0.135400640077266</v>
+        <v>1.67530296586662</v>
       </c>
       <c r="S69" t="n">
-        <v>11.275</v>
+        <v>0.293462617725086</v>
       </c>
       <c r="T69" t="n">
-        <v>0.286865241300975</v>
+        <v>1226.89242424242</v>
       </c>
       <c r="U69" t="n">
-        <v>1.67530296586662</v>
-      </c>
-      <c r="V69" t="n">
-        <v>0.293462617725086</v>
-      </c>
-      <c r="W69" t="n">
-        <v>1226.89242424242</v>
-      </c>
-      <c r="X69" t="n">
         <v>0.176682430248647</v>
       </c>
     </row>
@@ -4072,37 +3050,25 @@
           <t>FAR TAS W21-03-1MgmtStandardCvCesario</t>
         </is>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="3" t="n">
         <v>44347</v>
       </c>
       <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Cesario</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="J70" t="n">
+        <v>154.375</v>
+      </c>
+      <c r="K70" t="n">
+        <v>7.93036096278095</v>
+      </c>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="n">
-        <v>154.375</v>
-      </c>
-      <c r="N70" t="n">
-        <v>7.93036096278095</v>
-      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
@@ -4110,9 +3076,6 @@
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4120,31 +3083,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvCesario</t>
         </is>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="3" t="n">
         <v>44404</v>
       </c>
       <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Cesario</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G71" t="n">
+      <c r="D71" t="n">
         <v>0.6274999999999999</v>
       </c>
-      <c r="H71" t="n">
+      <c r="E71" t="n">
         <v>0.0179698822107065</v>
       </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
@@ -4158,9 +3109,6 @@
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
-      <c r="W71" t="inlineStr"/>
-      <c r="X71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4168,31 +3116,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvCesario</t>
         </is>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="3" t="n">
         <v>44469</v>
       </c>
       <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Cesario</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G72" t="n">
+      <c r="D72" t="n">
         <v>0.865</v>
       </c>
-      <c r="H72" t="n">
+      <c r="E72" t="n">
         <v>0.00288675134594813</v>
       </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -4206,9 +3142,6 @@
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr"/>
-      <c r="W72" t="inlineStr"/>
-      <c r="X72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4216,31 +3149,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvCesario</t>
         </is>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="3" t="n">
         <v>44512</v>
       </c>
       <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Cesario</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G73" t="n">
+      <c r="D73" t="n">
         <v>0.7975</v>
       </c>
-      <c r="H73" t="n">
+      <c r="E73" t="n">
         <v>0.00250000000000001</v>
       </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
@@ -4254,9 +3175,6 @@
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr"/>
-      <c r="W73" t="inlineStr"/>
-      <c r="X73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4264,31 +3182,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvCesario</t>
         </is>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="3" t="n">
         <v>44543</v>
       </c>
       <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Cesario</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G74" t="n">
+      <c r="D74" t="n">
         <v>0.4875</v>
       </c>
-      <c r="H74" t="n">
+      <c r="E74" t="n">
         <v>0.0110867789130417</v>
       </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
@@ -4302,9 +3208,6 @@
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
-      <c r="W74" t="inlineStr"/>
-      <c r="X74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4312,7 +3215,7 @@
           <t>FAR TAS W21-03-1MgmtStandardCvCesario</t>
         </is>
       </c>
-      <c r="B75" s="1" t="n">
+      <c r="B75" s="3" t="n">
         <v>44565</v>
       </c>
       <c r="C75" t="inlineStr">
@@ -4320,27 +3223,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Cesario</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G75" t="n">
+      <c r="D75" t="n">
         <v>0.14</v>
       </c>
-      <c r="H75" t="n">
+      <c r="E75" t="n">
         <v>0</v>
       </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
@@ -4354,9 +3245,6 @@
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
-      <c r="W75" t="inlineStr"/>
-      <c r="X75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4364,7 +3252,7 @@
           <t>FAR TAS W21-03-1MgmtStandardCvCesario</t>
         </is>
       </c>
-      <c r="B76" s="1" t="n">
+      <c r="B76" s="3" t="n">
         <v>44581</v>
       </c>
       <c r="C76" t="inlineStr">
@@ -4372,57 +3260,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Cesario</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+      <c r="L76" t="n">
+        <v>76.48999999999999</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.403259221841235</v>
+      </c>
+      <c r="N76" t="n">
+        <v>11.925</v>
+      </c>
       <c r="O76" t="n">
-        <v>76.48999999999999</v>
+        <v>0.228673712233538</v>
       </c>
       <c r="P76" t="n">
-        <v>0.403259221841235</v>
+        <v>11.85</v>
       </c>
       <c r="Q76" t="n">
-        <v>11.925</v>
+        <v>0.259807621135332</v>
       </c>
       <c r="R76" t="n">
-        <v>0.228673712233538</v>
+        <v>1.30092400834361</v>
       </c>
       <c r="S76" t="n">
-        <v>11.85</v>
+        <v>0.193189075539669</v>
       </c>
       <c r="T76" t="n">
-        <v>0.259807621135332</v>
+        <v>1247.81308539945</v>
       </c>
       <c r="U76" t="n">
-        <v>1.30092400834361</v>
-      </c>
-      <c r="V76" t="n">
-        <v>0.193189075539669</v>
-      </c>
-      <c r="W76" t="n">
-        <v>1247.81308539945</v>
-      </c>
-      <c r="X76" t="n">
         <v>0.167365639308403</v>
       </c>
     </row>
@@ -4432,37 +3305,25 @@
           <t>FAR TAS W21-03-1MgmtStandardCvAnapurna</t>
         </is>
       </c>
-      <c r="B77" s="1" t="n">
+      <c r="B77" s="3" t="n">
         <v>44347</v>
       </c>
       <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+      <c r="J77" t="n">
+        <v>164.375</v>
+      </c>
+      <c r="K77" t="n">
+        <v>4.93446636763625</v>
+      </c>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="n">
-        <v>164.375</v>
-      </c>
-      <c r="N77" t="n">
-        <v>4.93446636763625</v>
-      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr"/>
@@ -4470,9 +3331,6 @@
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
-      <c r="W77" t="inlineStr"/>
-      <c r="X77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4480,31 +3338,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvAnapurna</t>
         </is>
       </c>
-      <c r="B78" s="1" t="n">
+      <c r="B78" s="3" t="n">
         <v>44404</v>
       </c>
       <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G78" t="n">
+      <c r="D78" t="n">
         <v>0.665</v>
       </c>
-      <c r="H78" t="n">
+      <c r="E78" t="n">
         <v>0.00645497224367904</v>
       </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
@@ -4518,9 +3364,6 @@
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
-      <c r="W78" t="inlineStr"/>
-      <c r="X78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4528,31 +3371,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvAnapurna</t>
         </is>
       </c>
-      <c r="B79" s="1" t="n">
+      <c r="B79" s="3" t="n">
         <v>44469</v>
       </c>
       <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G79" t="n">
+      <c r="D79" t="n">
         <v>0.8375</v>
       </c>
-      <c r="H79" t="n">
+      <c r="E79" t="n">
         <v>0.0025</v>
       </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
@@ -4566,9 +3397,6 @@
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
-      <c r="X79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4576,31 +3404,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvAnapurna</t>
         </is>
       </c>
-      <c r="B80" s="1" t="n">
+      <c r="B80" s="3" t="n">
         <v>44512</v>
       </c>
       <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G80" t="n">
+      <c r="D80" t="n">
         <v>0.765</v>
       </c>
-      <c r="H80" t="n">
+      <c r="E80" t="n">
         <v>0.00288675134594813</v>
       </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
@@ -4614,9 +3430,6 @@
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
-      <c r="X80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4624,31 +3437,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvAnapurna</t>
         </is>
       </c>
-      <c r="B81" s="1" t="n">
+      <c r="B81" s="3" t="n">
         <v>44543</v>
       </c>
       <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G81" t="n">
+      <c r="D81" t="n">
         <v>0.415</v>
       </c>
-      <c r="H81" t="n">
+      <c r="E81" t="n">
         <v>0.0119023807142381</v>
       </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
@@ -4662,9 +3463,6 @@
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
-      <c r="X81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4672,7 +3470,7 @@
           <t>FAR TAS W21-03-1MgmtStandardCvAnapurna</t>
         </is>
       </c>
-      <c r="B82" s="1" t="n">
+      <c r="B82" s="3" t="n">
         <v>44565</v>
       </c>
       <c r="C82" t="inlineStr">
@@ -4680,27 +3478,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G82" t="n">
+      <c r="D82" t="n">
         <v>0.125</v>
       </c>
-      <c r="H82" t="n">
+      <c r="E82" t="n">
         <v>0.00645497224367903</v>
       </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
@@ -4714,9 +3500,6 @@
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4724,7 +3507,7 @@
           <t>FAR TAS W21-03-1MgmtStandardCvAnapurna</t>
         </is>
       </c>
-      <c r="B83" s="1" t="n">
+      <c r="B83" s="3" t="n">
         <v>44581</v>
       </c>
       <c r="C83" t="inlineStr">
@@ -4732,57 +3515,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+      <c r="L83" t="n">
+        <v>76.5035</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.6047293471738669</v>
+      </c>
+      <c r="N83" t="n">
+        <v>11.925</v>
+      </c>
       <c r="O83" t="n">
-        <v>76.5035</v>
+        <v>0.271952814534679</v>
       </c>
       <c r="P83" t="n">
-        <v>0.6047293471738669</v>
+        <v>12.275</v>
       </c>
       <c r="Q83" t="n">
-        <v>11.925</v>
+        <v>0.286865241300975</v>
       </c>
       <c r="R83" t="n">
-        <v>0.271952814534679</v>
+        <v>2.56936509071191</v>
       </c>
       <c r="S83" t="n">
-        <v>12.275</v>
+        <v>0.567382586360359</v>
       </c>
       <c r="T83" t="n">
-        <v>0.286865241300975</v>
+        <v>1139.70071166208</v>
       </c>
       <c r="U83" t="n">
-        <v>2.56936509071191</v>
-      </c>
-      <c r="V83" t="n">
-        <v>0.567382586360359</v>
-      </c>
-      <c r="W83" t="n">
-        <v>1139.70071166208</v>
-      </c>
-      <c r="X83" t="n">
         <v>0.170893586685646</v>
       </c>
     </row>
@@ -4792,37 +3560,25 @@
           <t>FAR TAS W21-03-1MgmtStandardCvScepter</t>
         </is>
       </c>
-      <c r="B84" s="1" t="n">
+      <c r="B84" s="3" t="n">
         <v>44347</v>
       </c>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
+      <c r="J84" t="n">
+        <v>170.625</v>
+      </c>
+      <c r="K84" t="n">
+        <v>5.43666181279162</v>
+      </c>
       <c r="L84" t="inlineStr"/>
-      <c r="M84" t="n">
-        <v>170.625</v>
-      </c>
-      <c r="N84" t="n">
-        <v>5.43666181279162</v>
-      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
@@ -4830,9 +3586,6 @@
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4840,31 +3593,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvScepter</t>
         </is>
       </c>
-      <c r="B85" s="1" t="n">
+      <c r="B85" s="3" t="n">
         <v>44404</v>
       </c>
       <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G85" t="n">
+      <c r="D85" t="n">
         <v>0.5925</v>
       </c>
-      <c r="H85" t="n">
+      <c r="E85" t="n">
         <v>0.0125</v>
       </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
@@ -4878,9 +3619,6 @@
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
-      <c r="X85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4888,31 +3626,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvScepter</t>
         </is>
       </c>
-      <c r="B86" s="1" t="n">
+      <c r="B86" s="3" t="n">
         <v>44469</v>
       </c>
       <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G86" t="n">
+      <c r="D86" t="n">
         <v>0.835</v>
       </c>
-      <c r="H86" t="n">
+      <c r="E86" t="n">
         <v>0.00500000000000001</v>
       </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
@@ -4926,9 +3652,6 @@
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
-      <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
-      <c r="X86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4936,31 +3659,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvScepter</t>
         </is>
       </c>
-      <c r="B87" s="1" t="n">
+      <c r="B87" s="3" t="n">
         <v>44512</v>
       </c>
       <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G87" t="n">
+      <c r="D87" t="n">
         <v>0.735</v>
       </c>
-      <c r="H87" t="n">
+      <c r="E87" t="n">
         <v>0.00288675134594814</v>
       </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
@@ -4974,9 +3685,6 @@
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr"/>
-      <c r="W87" t="inlineStr"/>
-      <c r="X87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4984,31 +3692,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvScepter</t>
         </is>
       </c>
-      <c r="B88" s="1" t="n">
+      <c r="B88" s="3" t="n">
         <v>44543</v>
       </c>
       <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G88" t="n">
+      <c r="D88" t="n">
         <v>0.3375</v>
       </c>
-      <c r="H88" t="n">
+      <c r="E88" t="n">
         <v>0.008539125638299659</v>
       </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
@@ -5022,9 +3718,6 @@
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="inlineStr"/>
       <c r="U88" t="inlineStr"/>
-      <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
-      <c r="X88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5032,7 +3725,7 @@
           <t>FAR TAS W21-03-1MgmtStandardCvScepter</t>
         </is>
       </c>
-      <c r="B89" s="1" t="n">
+      <c r="B89" s="3" t="n">
         <v>44565</v>
       </c>
       <c r="C89" t="inlineStr">
@@ -5040,27 +3733,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G89" t="n">
+      <c r="D89" t="n">
         <v>0.1675</v>
       </c>
-      <c r="H89" t="n">
+      <c r="E89" t="n">
         <v>0.00478713553878169</v>
       </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
@@ -5074,9 +3755,6 @@
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr"/>
-      <c r="V89" t="inlineStr"/>
-      <c r="W89" t="inlineStr"/>
-      <c r="X89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5084,7 +3762,7 @@
           <t>FAR TAS W21-03-1MgmtStandardCvScepter</t>
         </is>
       </c>
-      <c r="B90" s="1" t="n">
+      <c r="B90" s="3" t="n">
         <v>44581</v>
       </c>
       <c r="C90" t="inlineStr">
@@ -5092,57 +3770,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+      <c r="L90" t="n">
+        <v>70.508</v>
+      </c>
+      <c r="M90" t="n">
+        <v>2.35783488254232</v>
+      </c>
+      <c r="N90" t="n">
+        <v>11.85</v>
+      </c>
       <c r="O90" t="n">
-        <v>70.508</v>
+        <v>0.155456317551481</v>
       </c>
       <c r="P90" t="n">
-        <v>2.35783488254232</v>
+        <v>15.35</v>
       </c>
       <c r="Q90" t="n">
-        <v>11.85</v>
+        <v>0.239791576165636</v>
       </c>
       <c r="R90" t="n">
-        <v>0.155456317551481</v>
+        <v>1.8799236785991</v>
       </c>
       <c r="S90" t="n">
-        <v>15.35</v>
+        <v>0.492998506427952</v>
       </c>
       <c r="T90" t="n">
-        <v>0.239791576165636</v>
+        <v>472.13729338843</v>
       </c>
       <c r="U90" t="n">
-        <v>1.8799236785991</v>
-      </c>
-      <c r="V90" t="n">
-        <v>0.492998506427952</v>
-      </c>
-      <c r="W90" t="n">
-        <v>472.13729338843</v>
-      </c>
-      <c r="X90" t="n">
         <v>0.0768812331745726</v>
       </c>
     </row>
@@ -5152,37 +3815,25 @@
           <t>FAR TAS W21-03-1MgmtStandardCvTabasco</t>
         </is>
       </c>
-      <c r="B91" s="1" t="n">
+      <c r="B91" s="3" t="n">
         <v>44347</v>
       </c>
       <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Tabasco</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+      <c r="J91" t="n">
+        <v>160</v>
+      </c>
+      <c r="K91" t="n">
+        <v>9.29829733517558</v>
+      </c>
       <c r="L91" t="inlineStr"/>
-      <c r="M91" t="n">
-        <v>160</v>
-      </c>
-      <c r="N91" t="n">
-        <v>9.29829733517558</v>
-      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr"/>
@@ -5190,9 +3841,6 @@
       <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr"/>
-      <c r="V91" t="inlineStr"/>
-      <c r="W91" t="inlineStr"/>
-      <c r="X91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5200,31 +3848,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvTabasco</t>
         </is>
       </c>
-      <c r="B92" s="1" t="n">
+      <c r="B92" s="3" t="n">
         <v>44404</v>
       </c>
       <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Tabasco</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G92" t="n">
+      <c r="D92" t="n">
         <v>0.555</v>
       </c>
-      <c r="H92" t="n">
+      <c r="E92" t="n">
         <v>0.0104083299973307</v>
       </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
@@ -5238,9 +3874,6 @@
       <c r="S92" t="inlineStr"/>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
-      <c r="V92" t="inlineStr"/>
-      <c r="W92" t="inlineStr"/>
-      <c r="X92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5248,31 +3881,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvTabasco</t>
         </is>
       </c>
-      <c r="B93" s="1" t="n">
+      <c r="B93" s="3" t="n">
         <v>44469</v>
       </c>
       <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Tabasco</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G93" t="n">
+      <c r="D93" t="n">
         <v>0.8425</v>
       </c>
-      <c r="H93" t="n">
+      <c r="E93" t="n">
         <v>0.00478713553878171</v>
       </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
@@ -5286,9 +3907,6 @@
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
-      <c r="V93" t="inlineStr"/>
-      <c r="W93" t="inlineStr"/>
-      <c r="X93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5296,31 +3914,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvTabasco</t>
         </is>
       </c>
-      <c r="B94" s="1" t="n">
+      <c r="B94" s="3" t="n">
         <v>44512</v>
       </c>
       <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Tabasco</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G94" t="n">
+      <c r="D94" t="n">
         <v>0.84</v>
       </c>
-      <c r="H94" t="n">
+      <c r="E94" t="n">
         <v>0.00408248290463863</v>
       </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
@@ -5334,9 +3940,6 @@
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
-      <c r="V94" t="inlineStr"/>
-      <c r="W94" t="inlineStr"/>
-      <c r="X94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5344,31 +3947,19 @@
           <t>FAR TAS W21-03-1MgmtStandardCvTabasco</t>
         </is>
       </c>
-      <c r="B95" s="1" t="n">
+      <c r="B95" s="3" t="n">
         <v>44543</v>
       </c>
       <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Tabasco</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G95" t="n">
+      <c r="D95" t="n">
         <v>0.6325</v>
       </c>
-      <c r="H95" t="n">
+      <c r="E95" t="n">
         <v>0.00629152869605895</v>
       </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
@@ -5382,9 +3973,6 @@
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr"/>
       <c r="U95" t="inlineStr"/>
-      <c r="V95" t="inlineStr"/>
-      <c r="W95" t="inlineStr"/>
-      <c r="X95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5392,7 +3980,7 @@
           <t>FAR TAS W21-03-1MgmtStandardCvTabasco</t>
         </is>
       </c>
-      <c r="B96" s="1" t="n">
+      <c r="B96" s="3" t="n">
         <v>44565</v>
       </c>
       <c r="C96" t="inlineStr">
@@ -5400,27 +3988,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Tabasco</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G96" t="n">
+      <c r="D96" t="n">
         <v>0.14</v>
       </c>
-      <c r="H96" t="n">
+      <c r="E96" t="n">
         <v>0.00408248290463863</v>
       </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
@@ -5434,9 +4010,6 @@
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
-      <c r="V96" t="inlineStr"/>
-      <c r="W96" t="inlineStr"/>
-      <c r="X96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5444,7 +4017,7 @@
           <t>FAR TAS W21-03-1MgmtStandardCvTabasco</t>
         </is>
       </c>
-      <c r="B97" s="1" t="n">
+      <c r="B97" s="3" t="n">
         <v>44581</v>
       </c>
       <c r="C97" t="inlineStr">
@@ -5452,57 +4025,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Tabasco</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+      <c r="L97" t="n">
+        <v>72.56399999999999</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.438676038400395</v>
+      </c>
+      <c r="N97" t="n">
+        <v>11.375</v>
+      </c>
       <c r="O97" t="n">
-        <v>72.56399999999999</v>
+        <v>0.275</v>
       </c>
       <c r="P97" t="n">
-        <v>0.438676038400395</v>
+        <v>10.3</v>
       </c>
       <c r="Q97" t="n">
-        <v>11.375</v>
+        <v>0.248327740429189</v>
       </c>
       <c r="R97" t="n">
-        <v>0.275</v>
+        <v>3.94054591999243</v>
       </c>
       <c r="S97" t="n">
-        <v>10.3</v>
+        <v>0.777306269756794</v>
       </c>
       <c r="T97" t="n">
-        <v>0.248327740429189</v>
+        <v>1107.29993112948</v>
       </c>
       <c r="U97" t="n">
-        <v>3.94054591999243</v>
-      </c>
-      <c r="V97" t="n">
-        <v>0.777306269756794</v>
-      </c>
-      <c r="W97" t="n">
-        <v>1107.29993112948</v>
-      </c>
-      <c r="X97" t="n">
         <v>0.174145405156706</v>
       </c>
     </row>
@@ -5512,31 +4070,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvBig Red</t>
         </is>
       </c>
-      <c r="B98" s="1" t="n">
+      <c r="B98" s="3" t="n">
         <v>44404</v>
       </c>
       <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Big Red</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G98" t="n">
+      <c r="D98" t="n">
         <v>0.58</v>
       </c>
-      <c r="H98" t="n">
+      <c r="E98" t="n">
         <v>0.0135400640077266</v>
       </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
@@ -5550,9 +4096,6 @@
       <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
-      <c r="V98" t="inlineStr"/>
-      <c r="W98" t="inlineStr"/>
-      <c r="X98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5560,33 +4103,21 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvBig Red</t>
         </is>
       </c>
-      <c r="B99" s="1" t="n">
+      <c r="B99" s="3" t="n">
         <v>44434</v>
       </c>
       <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Big Red</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="n">
+        <v>171.1875</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.10694320435789</v>
+      </c>
       <c r="H99" t="inlineStr"/>
-      <c r="I99" t="n">
-        <v>171.1875</v>
-      </c>
-      <c r="J99" t="n">
-        <v>0.10694320435789</v>
-      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
@@ -5598,9 +4129,6 @@
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
-      <c r="V99" t="inlineStr"/>
-      <c r="W99" t="inlineStr"/>
-      <c r="X99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5608,31 +4136,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvBig Red</t>
         </is>
       </c>
-      <c r="B100" s="1" t="n">
+      <c r="B100" s="3" t="n">
         <v>44469</v>
       </c>
       <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Big Red</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G100" t="n">
+      <c r="D100" t="n">
         <v>0.805</v>
       </c>
-      <c r="H100" t="n">
+      <c r="E100" t="n">
         <v>0.00645497224367902</v>
       </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
@@ -5646,9 +4162,6 @@
       <c r="S100" t="inlineStr"/>
       <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr"/>
-      <c r="V100" t="inlineStr"/>
-      <c r="W100" t="inlineStr"/>
-      <c r="X100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5656,31 +4169,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvBig Red</t>
         </is>
       </c>
-      <c r="B101" s="1" t="n">
+      <c r="B101" s="3" t="n">
         <v>44512</v>
       </c>
       <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Big Red</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G101" t="n">
+      <c r="D101" t="n">
         <v>0.7775</v>
       </c>
-      <c r="H101" t="n">
+      <c r="E101" t="n">
         <v>0.00250000000000001</v>
       </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
@@ -5694,9 +4195,6 @@
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="inlineStr"/>
       <c r="U101" t="inlineStr"/>
-      <c r="V101" t="inlineStr"/>
-      <c r="W101" t="inlineStr"/>
-      <c r="X101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5704,31 +4202,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvBig Red</t>
         </is>
       </c>
-      <c r="B102" s="1" t="n">
+      <c r="B102" s="3" t="n">
         <v>44543</v>
       </c>
       <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Big Red</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G102" t="n">
+      <c r="D102" t="n">
         <v>0.4875</v>
       </c>
-      <c r="H102" t="n">
+      <c r="E102" t="n">
         <v>0.00853912563829967</v>
       </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
@@ -5742,9 +4228,6 @@
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="inlineStr"/>
       <c r="U102" t="inlineStr"/>
-      <c r="V102" t="inlineStr"/>
-      <c r="W102" t="inlineStr"/>
-      <c r="X102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5752,7 +4235,7 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvBig Red</t>
         </is>
       </c>
-      <c r="B103" s="1" t="n">
+      <c r="B103" s="3" t="n">
         <v>44565</v>
       </c>
       <c r="C103" t="inlineStr">
@@ -5760,27 +4243,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Big Red</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G103" t="n">
+      <c r="D103" t="n">
         <v>0.125</v>
       </c>
-      <c r="H103" t="n">
+      <c r="E103" t="n">
         <v>0.005</v>
       </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
@@ -5794,9 +4265,6 @@
       <c r="S103" t="inlineStr"/>
       <c r="T103" t="inlineStr"/>
       <c r="U103" t="inlineStr"/>
-      <c r="V103" t="inlineStr"/>
-      <c r="W103" t="inlineStr"/>
-      <c r="X103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5804,7 +4272,7 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvBig Red</t>
         </is>
       </c>
-      <c r="B104" s="1" t="n">
+      <c r="B104" s="3" t="n">
         <v>44581</v>
       </c>
       <c r="C104" t="inlineStr">
@@ -5812,57 +4280,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Big Red</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
+      <c r="L104" t="n">
+        <v>78.346</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.415291865238571</v>
+      </c>
+      <c r="N104" t="n">
+        <v>12.425</v>
+      </c>
       <c r="O104" t="n">
-        <v>78.346</v>
+        <v>0.301039864469807</v>
       </c>
       <c r="P104" t="n">
-        <v>0.415291865238571</v>
+        <v>10.825</v>
       </c>
       <c r="Q104" t="n">
-        <v>12.425</v>
+        <v>0.311916121203548</v>
       </c>
       <c r="R104" t="n">
-        <v>0.301039864469807</v>
+        <v>1.42168168083222</v>
       </c>
       <c r="S104" t="n">
-        <v>10.825</v>
+        <v>0.339149856834285</v>
       </c>
       <c r="T104" t="n">
-        <v>0.311916121203548</v>
+        <v>1156.77448268106</v>
       </c>
       <c r="U104" t="n">
-        <v>1.42168168083222</v>
-      </c>
-      <c r="V104" t="n">
-        <v>0.339149856834285</v>
-      </c>
-      <c r="W104" t="n">
-        <v>1156.77448268106</v>
-      </c>
-      <c r="X104" t="n">
         <v>0.136129813074399</v>
       </c>
     </row>
@@ -5872,33 +4325,21 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvScepter</t>
         </is>
       </c>
-      <c r="B105" s="1" t="n">
+      <c r="B105" s="3" t="n">
         <v>44399</v>
       </c>
       <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="n">
+        <v>76.1875</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.0457048388211431</v>
+      </c>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="n">
-        <v>76.1875</v>
-      </c>
-      <c r="J105" t="n">
-        <v>0.0457048388211431</v>
-      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
@@ -5910,9 +4351,6 @@
       <c r="S105" t="inlineStr"/>
       <c r="T105" t="inlineStr"/>
       <c r="U105" t="inlineStr"/>
-      <c r="V105" t="inlineStr"/>
-      <c r="W105" t="inlineStr"/>
-      <c r="X105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5920,31 +4358,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvScepter</t>
         </is>
       </c>
-      <c r="B106" s="1" t="n">
+      <c r="B106" s="3" t="n">
         <v>44404</v>
       </c>
       <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G106" t="n">
+      <c r="D106" t="n">
         <v>0.305</v>
       </c>
-      <c r="H106" t="n">
+      <c r="E106" t="n">
         <v>0.016583123951777</v>
       </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
@@ -5958,9 +4384,6 @@
       <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr"/>
       <c r="U106" t="inlineStr"/>
-      <c r="V106" t="inlineStr"/>
-      <c r="W106" t="inlineStr"/>
-      <c r="X106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5968,31 +4391,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvScepter</t>
         </is>
       </c>
-      <c r="B107" s="1" t="n">
+      <c r="B107" s="3" t="n">
         <v>44469</v>
       </c>
       <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G107" t="n">
+      <c r="D107" t="n">
         <v>0.8225</v>
       </c>
-      <c r="H107" t="n">
+      <c r="E107" t="n">
         <v>0.0025</v>
       </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
@@ -6006,9 +4417,6 @@
       <c r="S107" t="inlineStr"/>
       <c r="T107" t="inlineStr"/>
       <c r="U107" t="inlineStr"/>
-      <c r="V107" t="inlineStr"/>
-      <c r="W107" t="inlineStr"/>
-      <c r="X107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6016,31 +4424,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvScepter</t>
         </is>
       </c>
-      <c r="B108" s="1" t="n">
+      <c r="B108" s="3" t="n">
         <v>44512</v>
       </c>
       <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G108" t="n">
+      <c r="D108" t="n">
         <v>0.7475000000000001</v>
       </c>
-      <c r="H108" t="n">
+      <c r="E108" t="n">
         <v>0.0047871355387817</v>
       </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
@@ -6054,9 +4450,6 @@
       <c r="S108" t="inlineStr"/>
       <c r="T108" t="inlineStr"/>
       <c r="U108" t="inlineStr"/>
-      <c r="V108" t="inlineStr"/>
-      <c r="W108" t="inlineStr"/>
-      <c r="X108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6064,31 +4457,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvScepter</t>
         </is>
       </c>
-      <c r="B109" s="1" t="n">
+      <c r="B109" s="3" t="n">
         <v>44543</v>
       </c>
       <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G109" t="n">
+      <c r="D109" t="n">
         <v>0.3375</v>
       </c>
-      <c r="H109" t="n">
+      <c r="E109" t="n">
         <v>0.0170171482138851</v>
       </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
@@ -6102,9 +4483,6 @@
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr"/>
       <c r="U109" t="inlineStr"/>
-      <c r="V109" t="inlineStr"/>
-      <c r="W109" t="inlineStr"/>
-      <c r="X109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6112,7 +4490,7 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvScepter</t>
         </is>
       </c>
-      <c r="B110" s="1" t="n">
+      <c r="B110" s="3" t="n">
         <v>44565</v>
       </c>
       <c r="C110" t="inlineStr">
@@ -6120,27 +4498,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G110" t="n">
+      <c r="D110" t="n">
         <v>0.17</v>
       </c>
-      <c r="H110" t="n">
+      <c r="E110" t="n">
         <v>0.00408248290463863</v>
       </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
@@ -6154,9 +4520,6 @@
       <c r="S110" t="inlineStr"/>
       <c r="T110" t="inlineStr"/>
       <c r="U110" t="inlineStr"/>
-      <c r="V110" t="inlineStr"/>
-      <c r="W110" t="inlineStr"/>
-      <c r="X110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6164,7 +4527,7 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvScepter</t>
         </is>
       </c>
-      <c r="B111" s="1" t="n">
+      <c r="B111" s="3" t="n">
         <v>44581</v>
       </c>
       <c r="C111" t="inlineStr">
@@ -6172,57 +4535,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
+      <c r="L111" t="n">
+        <v>71.191</v>
+      </c>
+      <c r="M111" t="n">
+        <v>3.08563667120202</v>
+      </c>
+      <c r="N111" t="n">
+        <v>12.125</v>
+      </c>
       <c r="O111" t="n">
-        <v>71.191</v>
+        <v>0.188745860881769</v>
       </c>
       <c r="P111" t="n">
-        <v>3.08563667120202</v>
+        <v>15.675</v>
       </c>
       <c r="Q111" t="n">
-        <v>12.125</v>
+        <v>0.154784796841723</v>
       </c>
       <c r="R111" t="n">
-        <v>0.188745860881769</v>
+        <v>1.30522253014813</v>
       </c>
       <c r="S111" t="n">
-        <v>15.675</v>
+        <v>0.545701995824197</v>
       </c>
       <c r="T111" t="n">
-        <v>0.154784796841723</v>
+        <v>466.146356275303</v>
       </c>
       <c r="U111" t="n">
-        <v>1.30522253014813</v>
-      </c>
-      <c r="V111" t="n">
-        <v>0.545701995824197</v>
-      </c>
-      <c r="W111" t="n">
-        <v>466.146356275303</v>
-      </c>
-      <c r="X111" t="n">
         <v>0.653428065946642</v>
       </c>
     </row>
@@ -6232,31 +4580,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvAnapurna</t>
         </is>
       </c>
-      <c r="B112" s="1" t="n">
+      <c r="B112" s="3" t="n">
         <v>44404</v>
       </c>
       <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G112" t="n">
+      <c r="D112" t="n">
         <v>0.6775</v>
       </c>
-      <c r="H112" t="n">
+      <c r="E112" t="n">
         <v>0.0149303940559741</v>
       </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
@@ -6270,9 +4606,6 @@
       <c r="S112" t="inlineStr"/>
       <c r="T112" t="inlineStr"/>
       <c r="U112" t="inlineStr"/>
-      <c r="V112" t="inlineStr"/>
-      <c r="W112" t="inlineStr"/>
-      <c r="X112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6280,33 +4613,21 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvAnapurna</t>
         </is>
       </c>
-      <c r="B113" s="1" t="n">
+      <c r="B113" s="3" t="n">
         <v>44434</v>
       </c>
       <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="n">
+        <v>184.3125</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0.188757933056247</v>
+      </c>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="n">
-        <v>184.3125</v>
-      </c>
-      <c r="J113" t="n">
-        <v>0.188757933056247</v>
-      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
@@ -6318,9 +4639,6 @@
       <c r="S113" t="inlineStr"/>
       <c r="T113" t="inlineStr"/>
       <c r="U113" t="inlineStr"/>
-      <c r="V113" t="inlineStr"/>
-      <c r="W113" t="inlineStr"/>
-      <c r="X113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6328,31 +4646,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvAnapurna</t>
         </is>
       </c>
-      <c r="B114" s="1" t="n">
+      <c r="B114" s="3" t="n">
         <v>44469</v>
       </c>
       <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G114" t="n">
+      <c r="D114" t="n">
         <v>0.7775</v>
       </c>
-      <c r="H114" t="n">
+      <c r="E114" t="n">
         <v>0.0047871355387817</v>
       </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
@@ -6366,9 +4672,6 @@
       <c r="S114" t="inlineStr"/>
       <c r="T114" t="inlineStr"/>
       <c r="U114" t="inlineStr"/>
-      <c r="V114" t="inlineStr"/>
-      <c r="W114" t="inlineStr"/>
-      <c r="X114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6376,31 +4679,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvAnapurna</t>
         </is>
       </c>
-      <c r="B115" s="1" t="n">
+      <c r="B115" s="3" t="n">
         <v>44512</v>
       </c>
       <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G115" t="n">
+      <c r="D115" t="n">
         <v>0.7475000000000001</v>
       </c>
-      <c r="H115" t="n">
+      <c r="E115" t="n">
         <v>0.00250000000000001</v>
       </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
@@ -6414,9 +4705,6 @@
       <c r="S115" t="inlineStr"/>
       <c r="T115" t="inlineStr"/>
       <c r="U115" t="inlineStr"/>
-      <c r="V115" t="inlineStr"/>
-      <c r="W115" t="inlineStr"/>
-      <c r="X115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6424,31 +4712,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvAnapurna</t>
         </is>
       </c>
-      <c r="B116" s="1" t="n">
+      <c r="B116" s="3" t="n">
         <v>44543</v>
       </c>
       <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G116" t="n">
+      <c r="D116" t="n">
         <v>0.4275</v>
       </c>
-      <c r="H116" t="n">
+      <c r="E116" t="n">
         <v>0.00853912563829967</v>
       </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
@@ -6462,9 +4738,6 @@
       <c r="S116" t="inlineStr"/>
       <c r="T116" t="inlineStr"/>
       <c r="U116" t="inlineStr"/>
-      <c r="V116" t="inlineStr"/>
-      <c r="W116" t="inlineStr"/>
-      <c r="X116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6472,7 +4745,7 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvAnapurna</t>
         </is>
       </c>
-      <c r="B117" s="1" t="n">
+      <c r="B117" s="3" t="n">
         <v>44565</v>
       </c>
       <c r="C117" t="inlineStr">
@@ -6480,27 +4753,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G117" t="n">
+      <c r="D117" t="n">
         <v>0.1225</v>
       </c>
-      <c r="H117" t="n">
+      <c r="E117" t="n">
         <v>0.0025</v>
       </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
@@ -6514,9 +4775,6 @@
       <c r="S117" t="inlineStr"/>
       <c r="T117" t="inlineStr"/>
       <c r="U117" t="inlineStr"/>
-      <c r="V117" t="inlineStr"/>
-      <c r="W117" t="inlineStr"/>
-      <c r="X117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6524,7 +4782,7 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvAnapurna</t>
         </is>
       </c>
-      <c r="B118" s="1" t="n">
+      <c r="B118" s="3" t="n">
         <v>44581</v>
       </c>
       <c r="C118" t="inlineStr">
@@ -6532,57 +4790,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
+      <c r="L118" t="n">
+        <v>77.36199999999999</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.167367858324109</v>
+      </c>
+      <c r="N118" t="n">
+        <v>11.875</v>
+      </c>
       <c r="O118" t="n">
-        <v>77.36199999999999</v>
+        <v>0.193110503770941</v>
       </c>
       <c r="P118" t="n">
-        <v>0.167367858324109</v>
+        <v>11.425</v>
       </c>
       <c r="Q118" t="n">
-        <v>11.875</v>
+        <v>0.09464847243000429</v>
       </c>
       <c r="R118" t="n">
-        <v>0.193110503770941</v>
+        <v>2.82562781128942</v>
       </c>
       <c r="S118" t="n">
-        <v>11.425</v>
+        <v>0.490137470954538</v>
       </c>
       <c r="T118" t="n">
-        <v>0.09464847243000429</v>
+        <v>1051.4701417004</v>
       </c>
       <c r="U118" t="n">
-        <v>2.82562781128942</v>
-      </c>
-      <c r="V118" t="n">
-        <v>0.490137470954538</v>
-      </c>
-      <c r="W118" t="n">
-        <v>1051.4701417004</v>
-      </c>
-      <c r="X118" t="n">
         <v>0.0928957481873153</v>
       </c>
     </row>
@@ -6592,33 +4835,21 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvTrojan</t>
         </is>
       </c>
-      <c r="B119" s="1" t="n">
+      <c r="B119" s="3" t="n">
         <v>44399</v>
       </c>
       <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="n">
+        <v>75.125</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.0249269766852434</v>
+      </c>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="n">
-        <v>75.125</v>
-      </c>
-      <c r="J119" t="n">
-        <v>0.0249269766852434</v>
-      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
@@ -6630,9 +4861,6 @@
       <c r="S119" t="inlineStr"/>
       <c r="T119" t="inlineStr"/>
       <c r="U119" t="inlineStr"/>
-      <c r="V119" t="inlineStr"/>
-      <c r="W119" t="inlineStr"/>
-      <c r="X119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6640,31 +4868,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvTrojan</t>
         </is>
       </c>
-      <c r="B120" s="1" t="n">
+      <c r="B120" s="3" t="n">
         <v>44404</v>
       </c>
       <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G120" t="n">
+      <c r="D120" t="n">
         <v>0.305</v>
       </c>
-      <c r="H120" t="n">
+      <c r="E120" t="n">
         <v>0.00288675134594813</v>
       </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
@@ -6678,9 +4894,6 @@
       <c r="S120" t="inlineStr"/>
       <c r="T120" t="inlineStr"/>
       <c r="U120" t="inlineStr"/>
-      <c r="V120" t="inlineStr"/>
-      <c r="W120" t="inlineStr"/>
-      <c r="X120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6688,31 +4901,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvTrojan</t>
         </is>
       </c>
-      <c r="B121" s="1" t="n">
+      <c r="B121" s="3" t="n">
         <v>44469</v>
       </c>
       <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G121" t="n">
+      <c r="D121" t="n">
         <v>0.825</v>
       </c>
-      <c r="H121" t="n">
+      <c r="E121" t="n">
         <v>0.00499999999999997</v>
       </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
@@ -6726,9 +4927,6 @@
       <c r="S121" t="inlineStr"/>
       <c r="T121" t="inlineStr"/>
       <c r="U121" t="inlineStr"/>
-      <c r="V121" t="inlineStr"/>
-      <c r="W121" t="inlineStr"/>
-      <c r="X121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6736,31 +4934,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvTrojan</t>
         </is>
       </c>
-      <c r="B122" s="1" t="n">
+      <c r="B122" s="3" t="n">
         <v>44512</v>
       </c>
       <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G122" t="n">
+      <c r="D122" t="n">
         <v>0.745</v>
       </c>
-      <c r="H122" t="n">
+      <c r="E122" t="n">
         <v>0.00866025403784439</v>
       </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
@@ -6774,9 +4960,6 @@
       <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr"/>
       <c r="U122" t="inlineStr"/>
-      <c r="V122" t="inlineStr"/>
-      <c r="W122" t="inlineStr"/>
-      <c r="X122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6784,31 +4967,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvTrojan</t>
         </is>
       </c>
-      <c r="B123" s="1" t="n">
+      <c r="B123" s="3" t="n">
         <v>44543</v>
       </c>
       <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G123" t="n">
+      <c r="D123" t="n">
         <v>0.36</v>
       </c>
-      <c r="H123" t="n">
+      <c r="E123" t="n">
         <v>0.0168325082306035</v>
       </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
@@ -6822,9 +4993,6 @@
       <c r="S123" t="inlineStr"/>
       <c r="T123" t="inlineStr"/>
       <c r="U123" t="inlineStr"/>
-      <c r="V123" t="inlineStr"/>
-      <c r="W123" t="inlineStr"/>
-      <c r="X123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6832,7 +5000,7 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvTrojan</t>
         </is>
       </c>
-      <c r="B124" s="1" t="n">
+      <c r="B124" s="3" t="n">
         <v>44565</v>
       </c>
       <c r="C124" t="inlineStr">
@@ -6840,27 +5008,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G124" t="n">
+      <c r="D124" t="n">
         <v>0.16</v>
       </c>
-      <c r="H124" t="n">
+      <c r="E124" t="n">
         <v>0.00408248290463863</v>
       </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
@@ -6874,9 +5030,6 @@
       <c r="S124" t="inlineStr"/>
       <c r="T124" t="inlineStr"/>
       <c r="U124" t="inlineStr"/>
-      <c r="V124" t="inlineStr"/>
-      <c r="W124" t="inlineStr"/>
-      <c r="X124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6884,7 +5037,7 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvTrojan</t>
         </is>
       </c>
-      <c r="B125" s="1" t="n">
+      <c r="B125" s="3" t="n">
         <v>44581</v>
       </c>
       <c r="C125" t="inlineStr">
@@ -6892,57 +5045,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
+      <c r="L125" t="n">
+        <v>72.6695</v>
+      </c>
+      <c r="M125" t="n">
+        <v>1.03765645406689</v>
+      </c>
+      <c r="N125" t="n">
+        <v>11.925</v>
+      </c>
       <c r="O125" t="n">
-        <v>72.6695</v>
+        <v>0.292617497767991</v>
       </c>
       <c r="P125" t="n">
-        <v>1.03765645406689</v>
+        <v>13.85</v>
       </c>
       <c r="Q125" t="n">
-        <v>11.925</v>
+        <v>0.337885582211888</v>
       </c>
       <c r="R125" t="n">
-        <v>0.292617497767991</v>
+        <v>1.69605830655938</v>
       </c>
       <c r="S125" t="n">
-        <v>13.85</v>
+        <v>0.468084284009114</v>
       </c>
       <c r="T125" t="n">
-        <v>0.337885582211888</v>
+        <v>612.1414910111411</v>
       </c>
       <c r="U125" t="n">
-        <v>1.69605830655938</v>
-      </c>
-      <c r="V125" t="n">
-        <v>0.468084284009114</v>
-      </c>
-      <c r="W125" t="n">
-        <v>612.1414910111411</v>
-      </c>
-      <c r="X125" t="n">
         <v>0.316333910162313</v>
       </c>
     </row>
@@ -6952,31 +5090,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvTabasco</t>
         </is>
       </c>
-      <c r="B126" s="1" t="n">
+      <c r="B126" s="3" t="n">
         <v>44404</v>
       </c>
       <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Tabasco</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G126" t="n">
+      <c r="D126" t="n">
         <v>0.556666666666667</v>
       </c>
-      <c r="H126" t="n">
+      <c r="E126" t="n">
         <v>0.0133333333333333</v>
       </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
@@ -6990,9 +5116,6 @@
       <c r="S126" t="inlineStr"/>
       <c r="T126" t="inlineStr"/>
       <c r="U126" t="inlineStr"/>
-      <c r="V126" t="inlineStr"/>
-      <c r="W126" t="inlineStr"/>
-      <c r="X126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7000,33 +5123,21 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvTabasco</t>
         </is>
       </c>
-      <c r="B127" s="1" t="n">
+      <c r="B127" s="3" t="n">
         <v>44434</v>
       </c>
       <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Tabasco</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="n">
+        <v>93.0625</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.09258653047285011</v>
+      </c>
       <c r="H127" t="inlineStr"/>
-      <c r="I127" t="n">
-        <v>93.0625</v>
-      </c>
-      <c r="J127" t="n">
-        <v>0.09258653047285011</v>
-      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr"/>
@@ -7038,9 +5149,6 @@
       <c r="S127" t="inlineStr"/>
       <c r="T127" t="inlineStr"/>
       <c r="U127" t="inlineStr"/>
-      <c r="V127" t="inlineStr"/>
-      <c r="W127" t="inlineStr"/>
-      <c r="X127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7048,31 +5156,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvTabasco</t>
         </is>
       </c>
-      <c r="B128" s="1" t="n">
+      <c r="B128" s="3" t="n">
         <v>44469</v>
       </c>
       <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Tabasco</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G128" t="n">
+      <c r="D128" t="n">
         <v>0.8075</v>
       </c>
-      <c r="H128" t="n">
+      <c r="E128" t="n">
         <v>0.009464847243000439</v>
       </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
@@ -7086,9 +5182,6 @@
       <c r="S128" t="inlineStr"/>
       <c r="T128" t="inlineStr"/>
       <c r="U128" t="inlineStr"/>
-      <c r="V128" t="inlineStr"/>
-      <c r="W128" t="inlineStr"/>
-      <c r="X128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7096,31 +5189,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvTabasco</t>
         </is>
       </c>
-      <c r="B129" s="1" t="n">
+      <c r="B129" s="3" t="n">
         <v>44512</v>
       </c>
       <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Tabasco</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G129" t="n">
+      <c r="D129" t="n">
         <v>0.8375</v>
       </c>
-      <c r="H129" t="n">
+      <c r="E129" t="n">
         <v>0.00249999999999999</v>
       </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
@@ -7134,9 +5215,6 @@
       <c r="S129" t="inlineStr"/>
       <c r="T129" t="inlineStr"/>
       <c r="U129" t="inlineStr"/>
-      <c r="V129" t="inlineStr"/>
-      <c r="W129" t="inlineStr"/>
-      <c r="X129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7144,31 +5222,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvTabasco</t>
         </is>
       </c>
-      <c r="B130" s="1" t="n">
+      <c r="B130" s="3" t="n">
         <v>44543</v>
       </c>
       <c r="C130" t="inlineStr"/>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Tabasco</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G130" t="n">
+      <c r="D130" t="n">
         <v>0.61</v>
       </c>
-      <c r="H130" t="n">
+      <c r="E130" t="n">
         <v>0.0234520787991171</v>
       </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
@@ -7182,9 +5248,6 @@
       <c r="S130" t="inlineStr"/>
       <c r="T130" t="inlineStr"/>
       <c r="U130" t="inlineStr"/>
-      <c r="V130" t="inlineStr"/>
-      <c r="W130" t="inlineStr"/>
-      <c r="X130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7192,7 +5255,7 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvTabasco</t>
         </is>
       </c>
-      <c r="B131" s="1" t="n">
+      <c r="B131" s="3" t="n">
         <v>44565</v>
       </c>
       <c r="C131" t="inlineStr">
@@ -7200,27 +5263,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Tabasco</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G131" t="n">
+      <c r="D131" t="n">
         <v>0.1525</v>
       </c>
-      <c r="H131" t="n">
+      <c r="E131" t="n">
         <v>0.0075</v>
       </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
@@ -7234,9 +5285,6 @@
       <c r="S131" t="inlineStr"/>
       <c r="T131" t="inlineStr"/>
       <c r="U131" t="inlineStr"/>
-      <c r="V131" t="inlineStr"/>
-      <c r="W131" t="inlineStr"/>
-      <c r="X131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7244,7 +5292,7 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvTabasco</t>
         </is>
       </c>
-      <c r="B132" s="1" t="n">
+      <c r="B132" s="3" t="n">
         <v>44581</v>
       </c>
       <c r="C132" t="inlineStr">
@@ -7252,57 +5300,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Tabasco</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
+      <c r="L132" t="n">
+        <v>72.81399999999999</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.469829046923806</v>
+      </c>
+      <c r="N132" t="n">
+        <v>11.6</v>
+      </c>
       <c r="O132" t="n">
-        <v>72.81399999999999</v>
+        <v>0.37638632635454</v>
       </c>
       <c r="P132" t="n">
-        <v>0.469829046923806</v>
+        <v>10.2</v>
       </c>
       <c r="Q132" t="n">
-        <v>11.6</v>
+        <v>0.308220700148449</v>
       </c>
       <c r="R132" t="n">
-        <v>0.37638632635454</v>
+        <v>3.09617784137447</v>
       </c>
       <c r="S132" t="n">
-        <v>10.2</v>
+        <v>0.659552491819873</v>
       </c>
       <c r="T132" t="n">
-        <v>0.308220700148449</v>
+        <v>1051.53475033738</v>
       </c>
       <c r="U132" t="n">
-        <v>3.09617784137447</v>
-      </c>
-      <c r="V132" t="n">
-        <v>0.659552491819873</v>
-      </c>
-      <c r="W132" t="n">
-        <v>1051.53475033738</v>
-      </c>
-      <c r="X132" t="n">
         <v>0.118572530311714</v>
       </c>
     </row>
@@ -7312,31 +5345,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvAccroc</t>
         </is>
       </c>
-      <c r="B133" s="1" t="n">
+      <c r="B133" s="3" t="n">
         <v>44404</v>
       </c>
       <c r="C133" t="inlineStr"/>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G133" t="n">
+      <c r="D133" t="n">
         <v>0.6225000000000001</v>
       </c>
-      <c r="H133" t="n">
+      <c r="E133" t="n">
         <v>0.0221265300789196</v>
       </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
@@ -7350,9 +5371,6 @@
       <c r="S133" t="inlineStr"/>
       <c r="T133" t="inlineStr"/>
       <c r="U133" t="inlineStr"/>
-      <c r="V133" t="inlineStr"/>
-      <c r="W133" t="inlineStr"/>
-      <c r="X133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7360,33 +5378,21 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvAccroc</t>
         </is>
       </c>
-      <c r="B134" s="1" t="n">
+      <c r="B134" s="3" t="n">
         <v>44434</v>
       </c>
       <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="n">
+        <v>169.4375</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.19411222859899</v>
+      </c>
       <c r="H134" t="inlineStr"/>
-      <c r="I134" t="n">
-        <v>169.4375</v>
-      </c>
-      <c r="J134" t="n">
-        <v>0.19411222859899</v>
-      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr"/>
@@ -7398,9 +5404,6 @@
       <c r="S134" t="inlineStr"/>
       <c r="T134" t="inlineStr"/>
       <c r="U134" t="inlineStr"/>
-      <c r="V134" t="inlineStr"/>
-      <c r="W134" t="inlineStr"/>
-      <c r="X134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7408,31 +5411,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvAccroc</t>
         </is>
       </c>
-      <c r="B135" s="1" t="n">
+      <c r="B135" s="3" t="n">
         <v>44469</v>
       </c>
       <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G135" t="n">
+      <c r="D135" t="n">
         <v>0.8075</v>
       </c>
-      <c r="H135" t="n">
+      <c r="E135" t="n">
         <v>0.00749999999999998</v>
       </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
@@ -7446,9 +5437,6 @@
       <c r="S135" t="inlineStr"/>
       <c r="T135" t="inlineStr"/>
       <c r="U135" t="inlineStr"/>
-      <c r="V135" t="inlineStr"/>
-      <c r="W135" t="inlineStr"/>
-      <c r="X135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7456,31 +5444,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvAccroc</t>
         </is>
       </c>
-      <c r="B136" s="1" t="n">
+      <c r="B136" s="3" t="n">
         <v>44512</v>
       </c>
       <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G136" t="n">
+      <c r="D136" t="n">
         <v>0.7675</v>
       </c>
-      <c r="H136" t="n">
+      <c r="E136" t="n">
         <v>0.00249999999999999</v>
       </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
@@ -7494,9 +5470,6 @@
       <c r="S136" t="inlineStr"/>
       <c r="T136" t="inlineStr"/>
       <c r="U136" t="inlineStr"/>
-      <c r="V136" t="inlineStr"/>
-      <c r="W136" t="inlineStr"/>
-      <c r="X136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7504,31 +5477,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvAccroc</t>
         </is>
       </c>
-      <c r="B137" s="1" t="n">
+      <c r="B137" s="3" t="n">
         <v>44543</v>
       </c>
       <c r="C137" t="inlineStr"/>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G137" t="n">
+      <c r="D137" t="n">
         <v>0.3875</v>
       </c>
-      <c r="H137" t="n">
+      <c r="E137" t="n">
         <v>0.0025</v>
       </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
@@ -7542,9 +5503,6 @@
       <c r="S137" t="inlineStr"/>
       <c r="T137" t="inlineStr"/>
       <c r="U137" t="inlineStr"/>
-      <c r="V137" t="inlineStr"/>
-      <c r="W137" t="inlineStr"/>
-      <c r="X137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7552,7 +5510,7 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvAccroc</t>
         </is>
       </c>
-      <c r="B138" s="1" t="n">
+      <c r="B138" s="3" t="n">
         <v>44565</v>
       </c>
       <c r="C138" t="inlineStr">
@@ -7560,27 +5518,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G138" t="n">
+      <c r="D138" t="n">
         <v>0.125</v>
       </c>
-      <c r="H138" t="n">
+      <c r="E138" t="n">
         <v>0.00288675134594813</v>
       </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
@@ -7594,9 +5540,6 @@
       <c r="S138" t="inlineStr"/>
       <c r="T138" t="inlineStr"/>
       <c r="U138" t="inlineStr"/>
-      <c r="V138" t="inlineStr"/>
-      <c r="W138" t="inlineStr"/>
-      <c r="X138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7604,7 +5547,7 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvAccroc</t>
         </is>
       </c>
-      <c r="B139" s="1" t="n">
+      <c r="B139" s="3" t="n">
         <v>44581</v>
       </c>
       <c r="C139" t="inlineStr">
@@ -7612,57 +5555,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
+      <c r="L139" t="n">
+        <v>75.53449999999999</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.374069846419089</v>
+      </c>
+      <c r="N139" t="n">
+        <v>12</v>
+      </c>
       <c r="O139" t="n">
-        <v>75.53449999999999</v>
+        <v>0.324037034920393</v>
       </c>
       <c r="P139" t="n">
-        <v>0.374069846419089</v>
+        <v>10.8</v>
       </c>
       <c r="Q139" t="n">
-        <v>12</v>
+        <v>0.329140294302192</v>
       </c>
       <c r="R139" t="n">
-        <v>0.324037034920393</v>
+        <v>1.40098078202416</v>
       </c>
       <c r="S139" t="n">
-        <v>10.8</v>
+        <v>0.35403274048193</v>
       </c>
       <c r="T139" t="n">
-        <v>0.329140294302192</v>
+        <v>1089.48398560504</v>
       </c>
       <c r="U139" t="n">
-        <v>1.40098078202416</v>
-      </c>
-      <c r="V139" t="n">
-        <v>0.35403274048193</v>
-      </c>
-      <c r="W139" t="n">
-        <v>1089.48398560504</v>
-      </c>
-      <c r="X139" t="n">
         <v>0.113376856204203</v>
       </c>
     </row>
@@ -7672,31 +5600,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvCesario</t>
         </is>
       </c>
-      <c r="B140" s="1" t="n">
+      <c r="B140" s="3" t="n">
         <v>44404</v>
       </c>
       <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Cesario</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G140" t="n">
+      <c r="D140" t="n">
         <v>0.64</v>
       </c>
-      <c r="H140" t="n">
+      <c r="E140" t="n">
         <v>0.0147196014438798</v>
       </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
@@ -7710,9 +5626,6 @@
       <c r="S140" t="inlineStr"/>
       <c r="T140" t="inlineStr"/>
       <c r="U140" t="inlineStr"/>
-      <c r="V140" t="inlineStr"/>
-      <c r="W140" t="inlineStr"/>
-      <c r="X140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7720,33 +5633,21 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvCesario</t>
         </is>
       </c>
-      <c r="B141" s="1" t="n">
+      <c r="B141" s="3" t="n">
         <v>44434</v>
       </c>
       <c r="C141" t="inlineStr"/>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Cesario</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr"/>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="n">
+        <v>190.125</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.127681651644497</v>
+      </c>
       <c r="H141" t="inlineStr"/>
-      <c r="I141" t="n">
-        <v>190.125</v>
-      </c>
-      <c r="J141" t="n">
-        <v>0.127681651644497</v>
-      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
@@ -7758,9 +5659,6 @@
       <c r="S141" t="inlineStr"/>
       <c r="T141" t="inlineStr"/>
       <c r="U141" t="inlineStr"/>
-      <c r="V141" t="inlineStr"/>
-      <c r="W141" t="inlineStr"/>
-      <c r="X141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7768,31 +5666,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvCesario</t>
         </is>
       </c>
-      <c r="B142" s="1" t="n">
+      <c r="B142" s="3" t="n">
         <v>44469</v>
       </c>
       <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Cesario</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G142" t="n">
+      <c r="D142" t="n">
         <v>0.8225</v>
       </c>
-      <c r="H142" t="n">
+      <c r="E142" t="n">
         <v>0.00478713553878167</v>
       </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
@@ -7806,9 +5692,6 @@
       <c r="S142" t="inlineStr"/>
       <c r="T142" t="inlineStr"/>
       <c r="U142" t="inlineStr"/>
-      <c r="V142" t="inlineStr"/>
-      <c r="W142" t="inlineStr"/>
-      <c r="X142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7816,31 +5699,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvCesario</t>
         </is>
       </c>
-      <c r="B143" s="1" t="n">
+      <c r="B143" s="3" t="n">
         <v>44512</v>
       </c>
       <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Cesario</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G143" t="n">
+      <c r="D143" t="n">
         <v>0.78</v>
       </c>
-      <c r="H143" t="n">
+      <c r="E143" t="n">
         <v>0.00707106781186548</v>
       </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
@@ -7854,9 +5725,6 @@
       <c r="S143" t="inlineStr"/>
       <c r="T143" t="inlineStr"/>
       <c r="U143" t="inlineStr"/>
-      <c r="V143" t="inlineStr"/>
-      <c r="W143" t="inlineStr"/>
-      <c r="X143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7864,31 +5732,19 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvCesario</t>
         </is>
       </c>
-      <c r="B144" s="1" t="n">
+      <c r="B144" s="3" t="n">
         <v>44543</v>
       </c>
       <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Cesario</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G144" t="n">
+      <c r="D144" t="n">
         <v>0.4875</v>
       </c>
-      <c r="H144" t="n">
+      <c r="E144" t="n">
         <v>0.019737865470545</v>
       </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
@@ -7902,9 +5758,6 @@
       <c r="S144" t="inlineStr"/>
       <c r="T144" t="inlineStr"/>
       <c r="U144" t="inlineStr"/>
-      <c r="V144" t="inlineStr"/>
-      <c r="W144" t="inlineStr"/>
-      <c r="X144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7912,7 +5765,7 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvCesario</t>
         </is>
       </c>
-      <c r="B145" s="1" t="n">
+      <c r="B145" s="3" t="n">
         <v>44565</v>
       </c>
       <c r="C145" t="inlineStr">
@@ -7920,27 +5773,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Cesario</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G145" t="n">
+      <c r="D145" t="n">
         <v>0.1275</v>
       </c>
-      <c r="H145" t="n">
+      <c r="E145" t="n">
         <v>0.00629152869605896</v>
       </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
@@ -7954,9 +5795,6 @@
       <c r="S145" t="inlineStr"/>
       <c r="T145" t="inlineStr"/>
       <c r="U145" t="inlineStr"/>
-      <c r="V145" t="inlineStr"/>
-      <c r="W145" t="inlineStr"/>
-      <c r="X145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7964,7 +5802,7 @@
           <t>FAR TAS W21-03-1MgmtGrazedCvCesario</t>
         </is>
       </c>
-      <c r="B146" s="1" t="n">
+      <c r="B146" s="3" t="n">
         <v>44581</v>
       </c>
       <c r="C146" t="inlineStr">
@@ -7972,57 +5810,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Cesario</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
+      <c r="L146" t="n">
+        <v>76.8865</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0.437108968107493</v>
+      </c>
+      <c r="N146" t="n">
+        <v>12.1</v>
+      </c>
       <c r="O146" t="n">
-        <v>76.8865</v>
+        <v>0.147196014438797</v>
       </c>
       <c r="P146" t="n">
-        <v>0.437108968107493</v>
+        <v>10.925</v>
       </c>
       <c r="Q146" t="n">
-        <v>12.1</v>
+        <v>0.239356776939085</v>
       </c>
       <c r="R146" t="n">
-        <v>0.147196014438797</v>
+        <v>1.06471091345007</v>
       </c>
       <c r="S146" t="n">
-        <v>10.925</v>
+        <v>0.13162530306717</v>
       </c>
       <c r="T146" t="n">
-        <v>0.239356776939085</v>
+        <v>1183.7585919928</v>
       </c>
       <c r="U146" t="n">
-        <v>1.06471091345007</v>
-      </c>
-      <c r="V146" t="n">
-        <v>0.13162530306717</v>
-      </c>
-      <c r="W146" t="n">
-        <v>1183.7585919928</v>
-      </c>
-      <c r="X146" t="n">
         <v>0.131437704081833</v>
       </c>
     </row>
